--- a/relatorio_D1_exec2022-01-02_dado2022-01-01.xlsx
+++ b/relatorio_D1_exec2022-01-02_dado2022-01-01.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,37 +28,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F1F1F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -79,7 +62,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -87,63 +70,36 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,7 +475,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Relatório D-1 · Produtos Vendidos</t>
@@ -533,14 +489,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  INSIGHT:  No dado de 2022-01-01 (D-1), o produto líder foi P0014 (Electronics) com 962 un. Os 3 primeiros concentram 17% das vendas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>No dado de 2022-01-01 (D-1), o produto líder foi P0014 (Electronics) com 962 un. Os 3 primeiros concentram 17% das vendas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Produto</t>
@@ -568,1539 +524,1539 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>P0014</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6" t="n">
         <v>962</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>73436.83</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>C7/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>P0015</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <v>810</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>52478.25</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="D8" s="7" t="n">
+        <v>52478.24999999999</v>
+      </c>
+      <c r="E8" s="8">
         <f>C8/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>P0002</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6" t="n">
         <v>619</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>30942.66</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>C9/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>P0019</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="6" t="n">
         <v>506</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7" t="n">
         <v>25483.75</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f>C10/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>P0001</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>495</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="7" t="n">
         <v>19528.3</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f>C11/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>P0020</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>471</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="7" t="n">
         <v>36579.54</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <f>C12/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>P0006</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>467</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="7" t="n">
         <v>32976.31</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <f>C13/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>P0016</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>441</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="7" t="n">
         <v>42928.9</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f>C14/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>P0017</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>417</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="7" t="n">
         <v>37648.31</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <f>C15/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P0007</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>393</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="7" t="n">
         <v>35814.09</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f>C16/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>P0006</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>382</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="7" t="n">
         <v>15795.7</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <f>C17/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>P0017</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>373</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="7" t="n">
         <v>4367.83</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <f>C18/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>P0008</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>364</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="7" t="n">
         <v>13930.27</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <f>C19/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>P0005</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>346</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>33783.81</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <f>C20/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>P0003</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>344</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>30726.08</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <f>C21/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>P0008</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>312</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>30572.88</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <f>C22/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>P0013</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>311</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>24277.86</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <f>C23/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>P0004</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>15231</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="8">
         <f>C24/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>P0013</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>283</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="7" t="n">
         <v>16351.74</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="8">
         <f>C25/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>P0019</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>278</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="7" t="n">
         <v>21597.72</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="8">
         <f>C26/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>P0012</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>271</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="7" t="n">
         <v>21829.43</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <f>C27/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>P0016</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="7" t="n">
         <v>5584.5</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <f>C28/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>P0006</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="7" t="n">
         <v>21397.5</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <f>C29/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>P0015</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="7" t="n">
         <v>2885</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="8">
         <f>C30/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>P0017</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="6" t="n">
         <v>246</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="7" t="n">
         <v>5183.22</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <f>C31/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>P0011</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>232</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="7" t="n">
         <v>13036.08</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <f>C32/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>P0001</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="7" t="n">
         <v>7665.7</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="8">
         <f>C33/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>P0010</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="6" t="n">
         <v>230</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="7" t="n">
         <v>15715.26</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="8">
         <f>C34/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>P0007</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="6" t="n">
         <v>224</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="7" t="n">
         <v>15737.06</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="8">
         <f>C35/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>P0020</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="7" t="n">
         <v>11790.86</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="8">
         <f>C36/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>P0005</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="7" t="n">
         <v>16344</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="8">
         <f>C37/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>P0003</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="6" t="n">
         <v>182</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="7" t="n">
         <v>3723.72</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="8">
         <f>C38/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>P0009</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="6" t="n">
         <v>175</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="7" t="n">
         <v>3629.5</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="8">
         <f>C39/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>P0018</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="6" t="n">
         <v>168</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="7" t="n">
         <v>9548.24</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="8">
         <f>C40/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>P0005</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="6" t="n">
         <v>156</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="7" t="n">
         <v>12993.24</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <f>C41/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>P0004</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="6" t="n">
         <v>155</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="7" t="n">
         <v>6421.32</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="8">
         <f>C42/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>P0018</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="6" t="n">
         <v>151</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="7" t="n">
         <v>2955.07</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="8">
         <f>C43/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P0002</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>9451.5</v>
+      </c>
+      <c r="E44" s="8">
+        <f>C44/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>8779.5</v>
+      </c>
+      <c r="E45" s="8">
+        <f>C45/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>P0017</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C46" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D46" s="7" t="n">
         <v>4065</v>
       </c>
-      <c r="E44" s="9">
-        <f>C44/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="E46" s="8">
+        <f>C46/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P0007</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>6087.57</v>
+      </c>
+      <c r="E47" s="8">
+        <f>C47/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P0015</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>7727.1</v>
+      </c>
+      <c r="E48" s="8">
+        <f>C48/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P0010</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>7665.84</v>
+      </c>
+      <c r="E49" s="8">
+        <f>C49/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>6078.54</v>
+      </c>
+      <c r="E50" s="8">
+        <f>C50/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P0009</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>9640.469999999999</v>
+      </c>
+      <c r="E51" s="8">
+        <f>C51/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P0018</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>5238.72</v>
+      </c>
+      <c r="E52" s="8">
+        <f>C52/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P0007</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>3313.52</v>
+      </c>
+      <c r="E53" s="8">
+        <f>C53/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P0003</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>4324.32</v>
+      </c>
+      <c r="E54" s="8">
+        <f>C54/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P0018</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>6795.6</v>
+      </c>
+      <c r="E55" s="8">
+        <f>C55/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P0020</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>782</v>
+      </c>
+      <c r="E56" s="8">
+        <f>C56/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P0003</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1819.35</v>
+      </c>
+      <c r="E57" s="8">
+        <f>C57/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P0003</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>2314.88</v>
+      </c>
+      <c r="E58" s="8">
+        <f>C58/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P0016</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>2875.95</v>
+      </c>
+      <c r="E59" s="8">
+        <f>C59/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P0008</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>4379.88</v>
+      </c>
+      <c r="E60" s="8">
+        <f>C60/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>2522.64</v>
+      </c>
+      <c r="E61" s="8">
+        <f>C61/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P0013</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1831.2</v>
+      </c>
+      <c r="E62" s="8">
+        <f>C62/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P0009</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>2369.2</v>
+      </c>
+      <c r="E63" s="8">
+        <f>C63/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P0008</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1941.84</v>
+      </c>
+      <c r="E64" s="8">
+        <f>C64/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P0010</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1679.72</v>
+      </c>
+      <c r="E65" s="8">
+        <f>C65/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P0012</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>489</v>
+      </c>
+      <c r="E66" s="8">
+        <f>C66/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P0012</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E67" s="8">
+        <f>C67/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P0019</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1274.85</v>
+      </c>
+      <c r="E68" s="8">
+        <f>C68/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P0005</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>1030.96</v>
+      </c>
+      <c r="E69" s="8">
+        <f>C69/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P0014</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>937.3200000000001</v>
+      </c>
+      <c r="E70" s="8">
+        <f>C70/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P0016</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="E71" s="8">
+        <f>C71/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P0009</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>731.61</v>
+      </c>
+      <c r="E72" s="8">
+        <f>C72/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P0010</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>296.32</v>
+      </c>
+      <c r="E73" s="8">
+        <f>C73/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>P0002</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>9451.5</v>
-      </c>
-      <c r="E45" s="9">
-        <f>C45/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>P0011</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>8779.5</v>
-      </c>
-      <c r="E46" s="9">
-        <f>C46/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>P0007</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>131</v>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>6087.57</v>
-      </c>
-      <c r="E47" s="9">
-        <f>C47/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>P0015</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>129</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>7727.1</v>
-      </c>
-      <c r="E48" s="9">
-        <f>C48/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>P0010</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
-        <v>126</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>7665.84</v>
-      </c>
-      <c r="E49" s="9">
-        <f>C49/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>P0011</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="C74" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="E74" s="8">
+        <f>C74/$C$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P0004</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>6078.54</v>
-      </c>
-      <c r="E50" s="9">
-        <f>C50/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>P0009</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>112</v>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>9640.469999999999</v>
-      </c>
-      <c r="E51" s="9">
-        <f>C51/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>P0018</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>5238.72</v>
-      </c>
-      <c r="E52" s="9">
-        <f>C52/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>P0007</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>3313.52</v>
-      </c>
-      <c r="E53" s="9">
-        <f>C53/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>P0003</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>4324.32</v>
-      </c>
-      <c r="E54" s="9">
-        <f>C54/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>P0018</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>6795.6</v>
-      </c>
-      <c r="E55" s="9">
-        <f>C55/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>P0020</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>782</v>
-      </c>
-      <c r="E56" s="9">
-        <f>C56/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>P0003</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="D57" s="8" t="n">
-        <v>1819.35</v>
-      </c>
-      <c r="E57" s="9">
-        <f>C57/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>P0003</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>2314.88</v>
-      </c>
-      <c r="E58" s="9">
-        <f>C58/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>P0016</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="D59" s="8" t="n">
-        <v>2875.95</v>
-      </c>
-      <c r="E59" s="9">
-        <f>C59/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>P0008</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>4379.88</v>
-      </c>
-      <c r="E60" s="9">
-        <f>C60/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>P0011</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>2522.64</v>
-      </c>
-      <c r="E61" s="9">
-        <f>C61/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>P0013</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>1831.2</v>
-      </c>
-      <c r="E62" s="9">
-        <f>C62/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>P0009</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>2369.2</v>
-      </c>
-      <c r="E63" s="9">
-        <f>C63/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>P0008</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>1941.84</v>
-      </c>
-      <c r="E64" s="9">
-        <f>C64/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>P0010</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>1679.72</v>
-      </c>
-      <c r="E65" s="9">
-        <f>C65/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>P0012</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>489</v>
-      </c>
-      <c r="E66" s="9">
-        <f>C66/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>P0012</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>1398</v>
-      </c>
-      <c r="E67" s="9">
-        <f>C67/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>P0019</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Toys</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>1274.85</v>
-      </c>
-      <c r="E68" s="9">
-        <f>C68/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>P0005</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>1030.96</v>
-      </c>
-      <c r="E69" s="9">
-        <f>C69/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>P0014</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>937.3200000000001</v>
-      </c>
-      <c r="E70" s="9">
-        <f>C70/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>P0016</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="E71" s="9">
-        <f>C71/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>P0009</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>731.61</v>
-      </c>
-      <c r="E72" s="9">
-        <f>C72/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>P0010</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>296.32</v>
-      </c>
-      <c r="E73" s="9">
-        <f>C73/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>P0002</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="E74" s="9">
-        <f>C74/$C$76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>P0004</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="n">
+      <c r="C75" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="8" t="n">
+      <c r="D75" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="8">
         <f>C75/$C$76</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="11">
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" s="10">
         <f>SUM(C7:C75)</f>
         <v/>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="11">
         <f>SUM(D7:D75)</f>
         <v/>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="12">
         <f>SUM(E7:E75)</f>
         <v/>
       </c>
@@ -2109,7 +2065,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
